--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_180_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_180_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4351</v>
+        <v>7.2717</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6754</v>
+        <v>7.5456</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2402</v>
+        <v>-0.2738</v>
       </c>
       <c r="G2" t="n">
         <v>5.6687</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4809</v>
+        <v>-1.6443</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2592</v>
+        <v>-0.389</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2217</v>
+        <v>-1.2553</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4677</v>
+        <v>2.4125</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3524</v>
+        <v>3.7345</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8847</v>
+        <v>-1.322</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1716</v>
+        <v>0.2933</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4287</v>
+        <v>-0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7429</v>
+        <v>0.4015</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1013</v>
+        <v>1.8766</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6722</v>
+        <v>0.6288</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4291</v>
+        <v>1.2479</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9298</v>
+        <v>-1.5833</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2435</v>
+        <v>-0.7369</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6862</v>
+        <v>-0.8464</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3818</v>
+        <v>-1.1824</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1968</v>
+        <v>-0.4283</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5786</v>
+        <v>-0.7541</v>
       </c>
       <c r="V3" t="n">
         <v>1.214</v>
       </c>
       <c r="W3" t="n">
-        <v>1.214</v>
+        <v>2.2862</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6501</v>
+        <v>2.2057</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2745</v>
+        <v>3.1911</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6244</v>
+        <v>-0.9855</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2933</v>
+        <v>1.1716</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1081</v>
+        <v>0.4287</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4015</v>
+        <v>0.7429</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8766</v>
+        <v>3.1013</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6288</v>
+        <v>0.6722</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2479</v>
+        <v>2.4291</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5833</v>
+        <v>-1.9298</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7369</v>
+        <v>-0.2435</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8464</v>
+        <v>-1.6862</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9448</v>
+        <v>-0.6438</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8883</v>
+        <v>0.0356</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0565</v>
+        <v>-0.6794</v>
       </c>
       <c r="V4" t="n">
         <v>1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2862</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5884</v>
+        <v>2.0408</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9023</v>
+        <v>1.2876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.7533</v>
       </c>
       <c r="G5" t="n">
         <v>1.2135</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5709</v>
+        <v>-1.1185</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>-0.2869</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8988</v>
+        <v>-0.8316</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.11</v>
+        <v>-0.0353</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1942</v>
+        <v>0.2689</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3041</v>
@@ -922,10 +922,10 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.735</v>
+        <v>-0.6021</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2916</v>
+        <v>0.5589</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0266</v>
+        <v>-1.161</v>
       </c>
       <c r="G7" t="n">
         <v>0.3576</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.876</v>
+        <v>-0.7431</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>-0.1061</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5026</v>
+        <v>-0.637</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6949</v>
+        <v>-1.492</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8123</v>
+        <v>-0.3405</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-1.1515</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0898</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9067</v>
+        <v>-0.7038</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>-0.4911</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0562</v>
+        <v>-0.2126</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3943</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0585</v>
+        <v>-2.8505</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4978</v>
+        <v>-0.3279</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5563</v>
+        <v>-2.5227</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5711</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0461</v>
+        <v>-0.7459</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5351</v>
+        <v>-0.2906</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4889</v>
+        <v>-0.4553</v>
       </c>
       <c r="V9" t="n">
         <v>0.9304</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8049</v>
+        <v>-3.0527</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.9519</v>
       </c>
       <c r="F10" t="n">
         <v>-2.1008</v>
@@ -1234,10 +1234,10 @@
         <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7468</v>
+        <v>-0.9946</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3339</v>
+        <v>-0.5816</v>
       </c>
       <c r="U10" t="n">
         <v>-0.4129</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2493</v>
+        <v>-3.761</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8403</v>
+        <v>-0.4864</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.409</v>
+        <v>-3.2746</v>
       </c>
       <c r="G11" t="n">
         <v>-2.584</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2863</v>
+        <v>-0.798</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.963</v>
+        <v>-0.6091</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3233</v>
+        <v>-0.1889</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0026</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8641</v>
+        <v>-5.3923</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8226</v>
+        <v>-4.3508</v>
       </c>
       <c r="F12" t="n">
         <v>-1.0415</v>
@@ -1390,10 +1390,10 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9224</v>
+        <v>-1.4506</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1949</v>
+        <v>-0.7231</v>
       </c>
       <c r="U12" t="n">
         <v>-0.7275</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3754</v>
+        <v>-3.255199999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>9.008899999999997</v>
+        <v>10.1291</v>
       </c>
       <c r="F13" t="n">
         <v>-13.3842</v>
@@ -1468,13 +1468,13 @@
         <v>20.8758</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.1452</v>
+        <v>-10.025</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.990600000000001</v>
+        <v>-3.8702</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.154599999999999</v>
+        <v>-6.1546</v>
       </c>
       <c r="V13" t="n">
         <v>-2.255100000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3713</v>
+        <v>4.2508</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8849</v>
+        <v>4.5734</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.3227</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2567</v>
+        <v>3.3463</v>
       </c>
       <c r="H14" t="n">
-        <v>0.618</v>
+        <v>-3.5328</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3613</v>
+        <v>6.8791</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0296</v>
+        <v>4.4474</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0727</v>
+        <v>-2.9101</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9569</v>
+        <v>7.3575</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7729</v>
+        <v>-1.1011</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4547</v>
+        <v>-0.6227</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3182</v>
+        <v>-0.4783</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>4.9702</v>
+        <v>1.8143</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8887</v>
+        <v>1.2858</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0816</v>
+        <v>0.5285</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4577</v>
+        <v>3.9422</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0145</v>
+        <v>3.7786</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4432</v>
+        <v>0.1636</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2062</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9808</v>
+        <v>1.4653</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6449</v>
+        <v>0.409</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3359</v>
+        <v>1.0563</v>
       </c>
       <c r="V15" t="n">
         <v>3.6109</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2995</v>
+        <v>3.6926</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8609</v>
+        <v>4.1532</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5614</v>
+        <v>-0.4606</v>
       </c>
       <c r="G16" t="n">
         <v>0.9713000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4183</v>
+        <v>1.8115</v>
       </c>
       <c r="T16" t="n">
-        <v>2.084</v>
+        <v>1.3763</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3343</v>
+        <v>0.4351</v>
       </c>
       <c r="V16" t="n">
         <v>0.6778999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7352</v>
+        <v>3.3497</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3939</v>
+        <v>3.9977</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6587</v>
+        <v>-0.648</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3463</v>
+        <v>0.2567</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.5328</v>
+        <v>0.618</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8791</v>
+        <v>-0.3613</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4474</v>
+        <v>2.0296</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.9101</v>
+        <v>1.0727</v>
       </c>
       <c r="L17" t="n">
-        <v>7.3575</v>
+        <v>0.9569</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1011</v>
+        <v>-1.7729</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6227</v>
+        <v>-0.4547</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4783</v>
+        <v>-1.3182</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2987</v>
+        <v>2.9486</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1063</v>
+        <v>2.0014</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1924</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3647</v>
+        <v>0.2309</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3016</v>
+        <v>0.9319</v>
       </c>
       <c r="G18" t="n">
         <v>0.344</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1804</v>
+        <v>1.0466</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0589</v>
+        <v>0.177</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2393</v>
+        <v>0.8696</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.6503</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2279</v>
+        <v>-0.1099</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6748</v>
+        <v>-0.5404</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0208</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1344</v>
+        <v>0.118</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U19" t="n">
-        <v>0.239</v>
+        <v>0.3734</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2836</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6573</v>
+        <v>-1.1969</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4365</v>
+        <v>1.6724</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0938</v>
+        <v>-2.8693</v>
       </c>
       <c r="G20" t="n">
         <v>1.1844</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5834</v>
+        <v>1.0438</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2047</v>
+        <v>0.4406</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3787</v>
+        <v>0.6032</v>
       </c>
       <c r="V20" t="n">
         <v>1.214</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2327</v>
+        <v>-2.0411</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5559</v>
+        <v>-2.32</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3232</v>
+        <v>0.2788</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9094</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3725</v>
+        <v>0.5641</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0589</v>
+        <v>0.177</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4314</v>
+        <v>0.387</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4231</v>
+        <v>-2.9127</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0987</v>
+        <v>-0.9807</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3244</v>
+        <v>-1.9319</v>
       </c>
       <c r="G22" t="n">
         <v>0.2756</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.539</v>
+        <v>-0.0286</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2403</v>
+        <v>0.1522</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6372</v>
+        <v>-3.5034</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3872</v>
+        <v>-0.6795</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.25</v>
+        <v>-2.8239</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5095</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0141</v>
+        <v>1.1479</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0158</v>
+        <v>0.7235</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0018</v>
+        <v>0.4244</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2862</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.375400000000001</v>
+        <v>5.161799999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>13.384</v>
+        <v>13.3841</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.008699999999999</v>
+        <v>-8.2225</v>
       </c>
       <c r="G24" t="n">
         <v>3.7324</v>
@@ -2323,16 +2323,16 @@
         <v>-20.8758</v>
       </c>
       <c r="R24" t="n">
-        <v>8.118499999999999</v>
+        <v>8.118500000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>11.145</v>
+        <v>11.9315</v>
       </c>
       <c r="T24" t="n">
-        <v>6.1545</v>
+        <v>6.154299999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>4.990499999999999</v>
+        <v>5.776800000000001</v>
       </c>
       <c r="V24" t="n">
         <v>2.2551</v>
@@ -2341,7 +2341,7 @@
         <v>10.0752</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.820099999999999</v>
+        <v>-7.820100000000001</v>
       </c>
     </row>
   </sheetData>
